--- a/public/sample_uploads/investor_kpi_mappings.xlsx
+++ b/public/sample_uploads/investor_kpi_mappings.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khushali\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F788777-CF3E-4FFE-B038-FFD383D232E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,18 +35,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t xml:space="preserve">Mandatory: 
 Enter the Portfolio company name- exactly as entered on the platform
@@ -55,51 +54,51 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Mandatory:
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
+          </rPr>
+          <t xml:space="preserve">Mandatory:
 The standardised name you would like to see on the platform</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t>Mandatory: The exact name reported on the excel in the 1st column</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Mandatory: Input category - Income Statement, Balance Sheet, Cash Flow Statement, Operational Metrics.
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
+          </rPr>
+          <t xml:space="preserve">Mandatory: Input category - Income Statement, Balance Sheet, Cash Flow Statement, Operational Metrics.
 Or - add a custom category to group KPIs into it</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t xml:space="preserve">Mandatory:
 Input whether the value will be - Numeric, Money, Percentage
@@ -107,91 +106,91 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Optional
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
+          </rPr>
+          <t xml:space="preserve">Optional
 Add a parent name to group KPIs. The parent name should be the exact standard kpi name given.
 For example - Revenue is the parent standard name and revenue segments (div A, div B etc) can be grouped under the parent
 The parent KPI has to be the first in chronology while updating the excel</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Optional
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
+          </rPr>
+          <t xml:space="preserve">Optional
 Add position to view relevant kpi. If not mentioned, will be displayed in the chronology of upload</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t>Optional to show KPIs in generated reports. Input yes/no.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t>Optional</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t>Optional</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>Optional
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
+          </rPr>
+          <t xml:space="preserve">Optional
 Input Yes if the values should to be aggregated, No otherwise.
 For example - Monthly revenue numbers can be tagged yes to cumulate to qrt ytd. Employee count should be tagged as no</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <sz val="10"/>
           </rPr>
           <t xml:space="preserve">Optional, input when Auto Fill is selected as Compute
 </t>
@@ -203,7 +202,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24" count="24">
   <si>
     <t>Stakeholder *</t>
   </si>
@@ -280,55 +279,55 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="1"/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="1"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -375,13 +374,13 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Normal 5" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 5" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16" count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -455,48 +454,48 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
           <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
                 <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
                 <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
           <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
@@ -556,7 +555,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
           <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -568,9 +567,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O18"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:mv="urn:schemas-microsoft-com:mac:vml">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12.1796875" customWidth="1"/>
     <col min="2" max="2" width="17.26953125" customWidth="1"/>
@@ -586,7 +585,7 @@
     <col min="16376" max="16384" width="10.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" customFormat="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,8 +631,11 @@
       <c r="O1" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P1" s="6" t="str">
+        <v>Source Sheet</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" customFormat="false">
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
@@ -673,7 +675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" customFormat="false">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="4"/>
@@ -683,7 +685,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" customFormat="false">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="4"/>
@@ -693,7 +695,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" customFormat="false">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="4"/>
@@ -703,7 +705,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" customFormat="false">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="4"/>
@@ -713,7 +715,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" customFormat="false">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="4"/>
@@ -723,7 +725,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" customFormat="false">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="4"/>
@@ -733,7 +735,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" customFormat="false">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="4"/>
@@ -743,7 +745,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" customFormat="false">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="4"/>
@@ -753,7 +755,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" customFormat="false">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="4"/>
@@ -763,7 +765,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" customFormat="false">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="4"/>
@@ -773,7 +775,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" customFormat="false">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="4"/>
@@ -783,7 +785,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" customFormat="false">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="4"/>
@@ -793,7 +795,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" customFormat="false">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4"/>
@@ -803,7 +805,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" customFormat="false">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4"/>
@@ -813,7 +815,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" customFormat="false">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="4"/>
@@ -823,7 +825,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" customFormat="false">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="4"/>
@@ -835,17 +837,17 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1000">
       <formula1>"NA,Cumulate,Forward fill,Compute"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{1697BA40-D840-4180-B769-2C34DB3849D7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576">
       <formula1>"numeric, percentage, money"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576" xr:uid="{4C2CA754-561B-4E04-9B30-5358558ABDD8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576">
       <formula1>"NA, millions, crores, lakhs, thousands"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576" xr:uid="{9A500943-1E68-4220-95A8-4F6651756079}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1:O1048576">
       <formula1>"NA, Report Date, Average Rate"</formula1>
     </dataValidation>
   </dataValidations>
